--- a/public/sample-data/06-cash-position-FY2026-27-P2-August.xlsx
+++ b/public/sample-data/06-cash-position-FY2026-27-P2-August.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t>Fund Code</t>
   </si>
@@ -40,10 +40,10 @@
     <t>1000</t>
   </si>
   <si>
+    <t>4100</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>4100</t>
   </si>
   <si>
     <t>3200</t>
@@ -471,51 +471,51 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>72000000</v>
+        <v>38325000</v>
       </c>
       <c r="C2">
-        <v>48500000</v>
+        <v>13370000</v>
       </c>
       <c r="D2">
-        <v>44200000</v>
+        <v>15834000</v>
       </c>
       <c r="E2">
-        <v>76300000</v>
+        <v>35861000</v>
       </c>
       <c r="F2">
         <v>12000000</v>
       </c>
-      <c r="G2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" t="s">
-        <v>9</v>
+      <c r="G2">
+        <v>2100000</v>
+      </c>
+      <c r="H2">
+        <v>21761000</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>1956550</v>
+      </c>
+      <c r="C3">
+        <v>423500</v>
+      </c>
+      <c r="D3">
+        <v>489060</v>
+      </c>
+      <c r="E3">
+        <v>1890990</v>
+      </c>
+      <c r="F3" t="s">
         <v>10</v>
       </c>
-      <c r="B3">
-        <v>1680000</v>
-      </c>
-      <c r="C3">
-        <v>210000</v>
-      </c>
-      <c r="D3">
-        <v>530000</v>
-      </c>
-      <c r="E3">
-        <v>1360000</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
       <c r="G3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -526,22 +526,22 @@
         <v>7300000</v>
       </c>
       <c r="C4">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>1900000</v>
+        <v>306000</v>
       </c>
       <c r="E4">
-        <v>9400000</v>
+        <v>6994000</v>
       </c>
       <c r="F4">
         <v>5000000</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
